--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.76570662560137</v>
+        <v>7.599427326660223</v>
       </c>
       <c r="D2" t="n">
-        <v>47.52868803267026</v>
+        <v>7.723411805308918</v>
       </c>
       <c r="E2" t="n">
-        <v>13.72948812500856</v>
+        <v>2.23104182031389</v>
       </c>
       <c r="F2" t="n">
-        <v>13.78339875464771</v>
+        <v>2.239802297630253</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.76696836054442</v>
+        <v>10.19963235858847</v>
       </c>
       <c r="D3" t="n">
-        <v>62.36141657747132</v>
+        <v>10.13373019383909</v>
       </c>
       <c r="E3" t="n">
-        <v>13.72948812500856</v>
+        <v>2.23104182031389</v>
       </c>
       <c r="F3" t="n">
-        <v>13.78339875464771</v>
+        <v>2.239802297630253</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.38469247861666</v>
+        <v>7.212512527775207</v>
       </c>
       <c r="D4" t="n">
-        <v>43.85710671938322</v>
+        <v>7.126779841899773</v>
       </c>
       <c r="E4" t="n">
-        <v>13.72948812500856</v>
+        <v>2.23104182031389</v>
       </c>
       <c r="F4" t="n">
-        <v>13.78339875464771</v>
+        <v>2.239802297630253</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.26801456314085</v>
+        <v>8.168552366510388</v>
       </c>
       <c r="D5" t="n">
-        <v>49.84120100062327</v>
+        <v>8.099195162601282</v>
       </c>
       <c r="E5" t="n">
-        <v>13.72948812500856</v>
+        <v>2.23104182031389</v>
       </c>
       <c r="F5" t="n">
-        <v>13.78339875464771</v>
+        <v>2.239802297630253</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.28197003727821</v>
+        <v>6.87082013105771</v>
       </c>
       <c r="D6" t="n">
-        <v>42.01781423295645</v>
+        <v>6.827894812855423</v>
       </c>
       <c r="E6" t="n">
-        <v>13.72948812500856</v>
+        <v>2.23104182031389</v>
       </c>
       <c r="F6" t="n">
-        <v>13.78339875464771</v>
+        <v>2.239802297630253</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.56080803261461</v>
+        <v>2.853631305299874</v>
       </c>
       <c r="D7" t="n">
-        <v>16.71123206247433</v>
+        <v>2.715575210152079</v>
       </c>
       <c r="E7" t="n">
-        <v>13.72948812500856</v>
+        <v>2.23104182031389</v>
       </c>
       <c r="F7" t="n">
-        <v>13.78339875464771</v>
+        <v>2.239802297630253</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.04862244818747</v>
+        <v>4.557901147830464</v>
       </c>
       <c r="D8" t="n">
-        <v>28.52061704803524</v>
+        <v>4.634600270305727</v>
       </c>
       <c r="E8" t="n">
-        <v>13.72948812500856</v>
+        <v>2.23104182031389</v>
       </c>
       <c r="F8" t="n">
-        <v>13.78339875464771</v>
+        <v>2.239802297630253</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
